--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel-microservice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EE72E50-C804-4966-8E62-58FAEDACA33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259DD952-D5A3-4AE0-8502-DC216A9A8BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DE393F96-EA1C-47DA-9775-8E21A8034909}"/>
   </bookViews>
@@ -51,7 +51,7 @@
     <t>Anna</t>
   </si>
   <si>
-    <t>Sam</t>
+    <t>Saurav</t>
   </si>
 </sst>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel-microservice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259DD952-D5A3-4AE0-8502-DC216A9A8BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97BA020-9F86-4527-873D-540278967F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DE393F96-EA1C-47DA-9775-8E21A8034909}"/>
   </bookViews>
@@ -48,10 +48,10 @@
     <t>John</t>
   </si>
   <si>
-    <t>Anna</t>
-  </si>
-  <si>
     <t>Saurav</t>
+  </si>
+  <si>
+    <t>Raj</t>
   </si>
 </sst>
 </file>
@@ -447,7 +447,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2">
         <v>85</v>
@@ -458,7 +458,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2">
         <v>80</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel-microservice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97BA020-9F86-4527-873D-540278967F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E705CD7-8E75-4B42-91AD-98DF09E6C19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DE393F96-EA1C-47DA-9775-8E21A8034909}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>id</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>Raj</t>
+  </si>
+  <si>
+    <t>krithika</t>
   </si>
 </sst>
 </file>
@@ -417,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489BB5B4-F6CF-48BD-9779-215320ED9D6D}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -464,6 +467,17 @@
         <v>80</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel-microservice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E705CD7-8E75-4B42-91AD-98DF09E6C19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FCCF3B-CF6A-4E7A-9794-567AD919AF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DE393F96-EA1C-47DA-9775-8E21A8034909}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>krithika</t>
+  </si>
+  <si>
+    <t>Vishaka</t>
   </si>
 </sst>
 </file>
@@ -420,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489BB5B4-F6CF-48BD-9779-215320ED9D6D}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -478,6 +481,17 @@
         <v>70</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel-microservice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FCCF3B-CF6A-4E7A-9794-567AD919AF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB120AB8-0D19-4A4C-AAD1-4C602526BC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DE393F96-EA1C-47DA-9775-8E21A8034909}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>id</t>
   </si>
@@ -58,6 +58,12 @@
   </si>
   <si>
     <t>Vishaka</t>
+  </si>
+  <si>
+    <t>Smita</t>
+  </si>
+  <si>
+    <t>Kamya</t>
   </si>
 </sst>
 </file>
@@ -423,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489BB5B4-F6CF-48BD-9779-215320ED9D6D}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -492,6 +498,28 @@
         <v>30</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
